--- a/output/2026-10-05_01_Malesia_Terengganu_Cleaning.xlsx
+++ b/output/2026-10-05_01_Malesia_Terengganu_Cleaning.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore autorizzato (non produttore) di macchine per pulizia/spazzamento stradale, municipale, industriale e aeroportuale, attivo dal 1996. Copertura dichiarata su tutta la Malesia tramite reparti vendita/ricambi/assistenza; nessun riscontro di sede o dealer specifico a Terengganu.</t>
+          <t>Distributore autorizzato (non produttore) di macchine per pulizia/spazzamento stradale, municipale, industriale e aeroportuale, attivo dal 1996. Copertura dichiarata su tutta la Malesia tramite reparti vendita/ricambi/assistenza; nessun riscontro di sede o dealer specifico a Terengganu. [DUPLICATO — vedi anche: 2026-10-02_17_Malesia_Pahang_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Presenza confermata solo in Selangor/Melaka/Pahang (Kuantan); nessuna evidenza diretta di rete distributori a copertura nazionale completa né di presenza/servizio specifico a Terengganu. La filiale di Kuantan (Pahang) è geograficamente vicina a Terengganu ma non costituisce prova di copertura dell'area target.</t>
+          <t>Presenza confermata solo in Selangor/Melaka/Pahang (Kuantan); nessuna evidenza diretta di rete distributori a copertura nazionale completa né di presenza/servizio specifico a Terengganu. La filiale di Kuantan (Pahang) è geograficamente vicina a Terengganu ma non costituisce prova di copertura dell'area target. [DUPLICATO — vedi anche: 2026-10-01_21_Malesia_Melaka_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -657,11 +657,9 @@
           <t>Cleaning - aspiratori wet&amp;dry, idropulitrici alta pressione, lavasciuga pavimenti (rivenditore autorizzato Karcher e Jetmaster)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rivenditore/distributore autorizzato di marchi Karcher e Jetmaster (aspiratori, idropulitrici, lavapavimenti) attivo dal 2007, con vendita online e consegna dichiarata in tutta la Malesia incluso supporto/garanzia locale. Nessuna sede fisica a Terengganu; telefono ed email diretti non reperiti da fonte verificabile, lasciati vuoti per non inventare dati.</t>
+          <t>Rivenditore/distributore autorizzato di marchi Karcher e Jetmaster (aspiratori, idropulitrici, lavapavimenti) attivo dal 2007, con vendita online e consegna dichiarata in tutta la Malesia incluso supporto/garanzia locale. Nessuna sede fisica a Terengganu; telefono ed email diretti non reperiti da fonte verificabile, lasciati vuoti per non inventare dati. [DUPLICATO — vedi anche: 2026-10-03_11_Malesia_Perlis_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
